--- a/artfynd/A 21553-2023 artfynd.xlsx
+++ b/artfynd/A 21553-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 21553-2023 artfynd.xlsx
+++ b/artfynd/A 21553-2023 artfynd.xlsx
@@ -2045,10 +2045,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119698195</v>
+        <v>119698250</v>
       </c>
       <c r="B14" t="n">
-        <v>91840</v>
+        <v>91463</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2057,25 +2057,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2085,10 +2085,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>777782</v>
+        <v>777772</v>
       </c>
       <c r="R14" t="n">
-        <v>7166733</v>
+        <v>7166742</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2157,10 +2157,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119698250</v>
+        <v>119698203</v>
       </c>
       <c r="B15" t="n">
-        <v>91463</v>
+        <v>91834</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2173,21 +2173,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>777772</v>
+        <v>777770</v>
       </c>
       <c r="R15" t="n">
-        <v>7166742</v>
+        <v>7166736</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2269,10 +2269,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119698203</v>
+        <v>119698334</v>
       </c>
       <c r="B16" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2281,38 +2281,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Killingberget, Killingberget, Vb</t>
+          <t>Basmyrberget, Basmyrberget, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>777770</v>
+        <v>777707</v>
       </c>
       <c r="R16" t="n">
-        <v>7166736</v>
+        <v>7166747</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2381,7 +2381,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119698334</v>
+        <v>119698195</v>
       </c>
       <c r="B17" t="n">
         <v>91840</v>
@@ -2417,14 +2417,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Basmyrberget, Basmyrberget, Vb</t>
+          <t>Killingberget, Killingberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>777707</v>
+        <v>777782</v>
       </c>
       <c r="R17" t="n">
-        <v>7166747</v>
+        <v>7166733</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 21553-2023 artfynd.xlsx
+++ b/artfynd/A 21553-2023 artfynd.xlsx
@@ -1933,10 +1933,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119698261</v>
+        <v>119698250</v>
       </c>
       <c r="B13" t="n">
-        <v>91852</v>
+        <v>91463</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1945,25 +1945,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4366</v>
+        <v>4745</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>777751</v>
+        <v>777772</v>
       </c>
       <c r="R13" t="n">
-        <v>7166747</v>
+        <v>7166742</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2045,10 +2045,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119698250</v>
+        <v>119698261</v>
       </c>
       <c r="B14" t="n">
-        <v>91463</v>
+        <v>91852</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2057,25 +2057,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4745</v>
+        <v>4366</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2085,10 +2085,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>777772</v>
+        <v>777751</v>
       </c>
       <c r="R14" t="n">
-        <v>7166742</v>
+        <v>7166747</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 21553-2023 artfynd.xlsx
+++ b/artfynd/A 21553-2023 artfynd.xlsx
@@ -1821,7 +1821,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119698410</v>
+        <v>119698195</v>
       </c>
       <c r="B12" t="n">
         <v>91840</v>
@@ -1857,14 +1857,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Basmyrberget, Basmyrberget, Vb</t>
+          <t>Killingberget, Killingberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>777656</v>
+        <v>777782</v>
       </c>
       <c r="R12" t="n">
-        <v>7166690</v>
+        <v>7166733</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1933,10 +1933,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119698250</v>
+        <v>119698261</v>
       </c>
       <c r="B13" t="n">
-        <v>91463</v>
+        <v>91852</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1945,25 +1945,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4745</v>
+        <v>4366</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>777772</v>
+        <v>777751</v>
       </c>
       <c r="R13" t="n">
-        <v>7166742</v>
+        <v>7166747</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2045,10 +2045,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119698261</v>
+        <v>119698203</v>
       </c>
       <c r="B14" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2057,25 +2057,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2085,10 +2085,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>777751</v>
+        <v>777770</v>
       </c>
       <c r="R14" t="n">
-        <v>7166747</v>
+        <v>7166736</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2157,10 +2157,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119698203</v>
+        <v>119698334</v>
       </c>
       <c r="B15" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2169,38 +2169,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Killingberget, Killingberget, Vb</t>
+          <t>Basmyrberget, Basmyrberget, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>777770</v>
+        <v>777707</v>
       </c>
       <c r="R15" t="n">
-        <v>7166736</v>
+        <v>7166747</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2269,10 +2269,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119698334</v>
+        <v>119698250</v>
       </c>
       <c r="B16" t="n">
-        <v>91840</v>
+        <v>91463</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2281,38 +2281,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Basmyrberget, Basmyrberget, Vb</t>
+          <t>Killingberget, Killingberget, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>777707</v>
+        <v>777772</v>
       </c>
       <c r="R16" t="n">
-        <v>7166747</v>
+        <v>7166742</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2381,7 +2381,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119698195</v>
+        <v>119698410</v>
       </c>
       <c r="B17" t="n">
         <v>91840</v>
@@ -2417,14 +2417,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Killingberget, Killingberget, Vb</t>
+          <t>Basmyrberget, Basmyrberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>777782</v>
+        <v>777656</v>
       </c>
       <c r="R17" t="n">
-        <v>7166733</v>
+        <v>7166690</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 21553-2023 artfynd.xlsx
+++ b/artfynd/A 21553-2023 artfynd.xlsx
@@ -1821,7 +1821,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119698195</v>
+        <v>119698410</v>
       </c>
       <c r="B12" t="n">
         <v>91840</v>
@@ -1857,14 +1857,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Killingberget, Killingberget, Vb</t>
+          <t>Basmyrberget, Basmyrberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>777782</v>
+        <v>777656</v>
       </c>
       <c r="R12" t="n">
-        <v>7166733</v>
+        <v>7166690</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1933,10 +1933,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119698261</v>
+        <v>119698195</v>
       </c>
       <c r="B13" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1949,21 +1949,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>777751</v>
+        <v>777782</v>
       </c>
       <c r="R13" t="n">
-        <v>7166747</v>
+        <v>7166733</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2045,10 +2045,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119698203</v>
+        <v>119698261</v>
       </c>
       <c r="B14" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2057,25 +2057,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2085,10 +2085,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>777770</v>
+        <v>777751</v>
       </c>
       <c r="R14" t="n">
-        <v>7166736</v>
+        <v>7166747</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2157,10 +2157,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119698334</v>
+        <v>119698203</v>
       </c>
       <c r="B15" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2169,38 +2169,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Basmyrberget, Basmyrberget, Vb</t>
+          <t>Killingberget, Killingberget, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>777707</v>
+        <v>777770</v>
       </c>
       <c r="R15" t="n">
-        <v>7166747</v>
+        <v>7166736</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2381,7 +2381,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119698410</v>
+        <v>119698334</v>
       </c>
       <c r="B17" t="n">
         <v>91840</v>
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>777656</v>
+        <v>777707</v>
       </c>
       <c r="R17" t="n">
-        <v>7166690</v>
+        <v>7166747</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
